--- a/data/sample/midhili/Midhili_ddm.xlsx
+++ b/data/sample/midhili/Midhili_ddm.xlsx
@@ -5,17 +5,20 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim\Desktop\test\ddm\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ibrahim\IBF-Analysis\data\sample\midhili\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DF7549-19D2-4C4B-B486-2A7FEDB5C549}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA82EB68-0840-447B-A1AE-378FBFE08FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="House" sheetId="2" r:id="rId1"/>
     <sheet name="Agriculture" sheetId="3" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Agriculture!$A$2:$H$100</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="126">
   <si>
     <t>Rajapur</t>
   </si>
@@ -72,9 +75,6 @@
     <t>Parshuram</t>
   </si>
   <si>
-    <t>Taltali</t>
-  </si>
-  <si>
     <t>Barguna Sadar</t>
   </si>
   <si>
@@ -96,18 +96,12 @@
     <t>Khulna</t>
   </si>
   <si>
-    <t>Raipur</t>
-  </si>
-  <si>
     <t>Ramganj</t>
   </si>
   <si>
     <t>Ramgati</t>
   </si>
   <si>
-    <t>Komolnagar</t>
-  </si>
-  <si>
     <t>Mirzaganj</t>
   </si>
   <si>
@@ -207,12 +201,6 @@
     <t>Phultala</t>
   </si>
   <si>
-    <t>Chalna Pourashava</t>
-  </si>
-  <si>
-    <t>Paikgacha Pourashava</t>
-  </si>
-  <si>
     <t>Mirsharai</t>
   </si>
   <si>
@@ -255,9 +243,6 @@
     <t>Banshkhali</t>
   </si>
   <si>
-    <t>City Corporation</t>
-  </si>
-  <si>
     <t>Zanjira</t>
   </si>
   <si>
@@ -288,9 +273,6 @@
     <t>Laksam</t>
   </si>
   <si>
-    <t>Chouddagram</t>
-  </si>
-  <si>
     <t>Chittagong</t>
   </si>
   <si>
@@ -427,6 +409,18 @@
   </si>
   <si>
     <t>Total_loss_amount_land</t>
+  </si>
+  <si>
+    <t>Taltoli</t>
+  </si>
+  <si>
+    <t>Chauddagram</t>
+  </si>
+  <si>
+    <t>Kamalnagar</t>
+  </si>
+  <si>
+    <t>Roypur</t>
   </si>
 </sst>
 </file>
@@ -502,14 +496,14 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92431B50-508F-416F-B0F6-34A43DD11A07}">
-  <dimension ref="A1:J103"/>
+  <dimension ref="A1:J100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -806,57 +800,57 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
+      <c r="C1" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -887,10 +881,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -902,7 +896,7 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <f t="shared" ref="F4:F67" si="0">C4+D4+E4</f>
+        <f t="shared" ref="F4:F65" si="0">C4+D4+E4</f>
         <v>2</v>
       </c>
       <c r="G4">
@@ -915,13 +909,13 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J67" si="1">G4+H4+I4</f>
+        <f t="shared" ref="J4:J65" si="1">G4+H4+I4</f>
         <v>100000</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -955,10 +949,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -989,10 +983,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -1023,10 +1017,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1057,10 +1051,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1091,7 +1085,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -1125,7 +1119,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -1159,7 +1153,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -1193,10 +1187,10 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1227,10 +1221,10 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1261,7 +1255,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -1295,7 +1289,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -1329,7 +1323,7 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -1363,10 +1357,10 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1397,10 +1391,10 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1431,7 +1425,7 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1465,10 +1459,10 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1499,10 +1493,10 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1533,7 +1527,7 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -1567,10 +1561,10 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1601,7 +1595,7 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -1635,10 +1629,10 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1669,10 +1663,10 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1703,10 +1697,10 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1737,10 +1731,10 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1771,10 +1765,10 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1805,10 +1799,10 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1839,10 +1833,10 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1873,10 +1867,10 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1907,10 +1901,10 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1941,10 +1935,10 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -1975,10 +1969,10 @@
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -2009,10 +2003,10 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -2021,11 +2015,11 @@
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -2034,16 +2028,16 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -2052,35 +2046,35 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="E38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="F38">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G38">
         <v>0</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>115</v>
       </c>
       <c r="J38">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -2089,11 +2083,11 @@
         <v>0</v>
       </c>
       <c r="E39">
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="F39">
         <f t="shared" si="0"/>
-        <v>30</v>
+        <v>75</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -2102,254 +2096,254 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>30</v>
+        <v>37.5</v>
       </c>
       <c r="J39">
         <f t="shared" si="1"/>
-        <v>30</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="E40">
-        <v>110</v>
+        <v>3</v>
       </c>
       <c r="F40">
         <f t="shared" si="0"/>
-        <v>160</v>
+        <v>7</v>
       </c>
       <c r="G40">
         <v>0</v>
       </c>
       <c r="H40">
-        <v>25</v>
+        <v>800000</v>
       </c>
       <c r="I40">
-        <v>115</v>
+        <v>500000</v>
       </c>
       <c r="J40">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>1300000</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E41">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="F41">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>35</v>
       </c>
       <c r="G41">
         <v>0</v>
       </c>
       <c r="H41">
-        <v>0</v>
+        <v>1000000</v>
       </c>
       <c r="I41">
-        <v>37.5</v>
+        <v>3000000</v>
       </c>
       <c r="J41">
         <f t="shared" si="1"/>
-        <v>37.5</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F42">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <v>0</v>
       </c>
       <c r="H42">
-        <v>800000</v>
+        <v>0</v>
       </c>
       <c r="I42">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="J42">
         <f t="shared" si="1"/>
-        <v>1300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E43">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="F43">
         <f t="shared" si="0"/>
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="G43">
         <v>0</v>
       </c>
       <c r="H43">
-        <v>1000000</v>
+        <v>1400000</v>
       </c>
       <c r="I43">
-        <v>3000000</v>
+        <v>300000</v>
       </c>
       <c r="J43">
         <f t="shared" si="1"/>
-        <v>4000000</v>
+        <v>1700000</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F44">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G44">
         <v>0</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>1600000</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>1900000</v>
       </c>
       <c r="J44">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3500000</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F45">
         <f t="shared" si="0"/>
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G45">
         <v>0</v>
       </c>
       <c r="H45">
-        <v>1400000</v>
+        <v>400000</v>
       </c>
       <c r="I45">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J45">
         <f t="shared" si="1"/>
-        <v>1700000</v>
+        <v>400000</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E46">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F46">
         <f t="shared" si="0"/>
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="G46">
         <v>0</v>
       </c>
       <c r="H46">
-        <v>1600000</v>
+        <v>3000000</v>
       </c>
       <c r="I46">
-        <v>1900000</v>
+        <v>1000000</v>
       </c>
       <c r="J46">
         <f t="shared" si="1"/>
-        <v>3500000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
@@ -2358,103 +2352,103 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F47">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="G47">
         <v>0</v>
       </c>
       <c r="H47">
-        <v>400000</v>
+        <v>2200000</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>3200000</v>
       </c>
       <c r="J47">
         <f t="shared" si="1"/>
-        <v>400000</v>
+        <v>5400000</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F48">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
       </c>
       <c r="H48">
-        <v>3000000</v>
+        <v>0</v>
       </c>
       <c r="I48">
-        <v>1000000</v>
+        <v>0</v>
       </c>
       <c r="J48">
         <f t="shared" si="1"/>
-        <v>4000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F49">
         <f t="shared" si="0"/>
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
       </c>
       <c r="H49">
-        <v>2200000</v>
+        <v>0</v>
       </c>
       <c r="I49">
-        <v>3200000</v>
+        <v>0</v>
       </c>
       <c r="J49">
         <f t="shared" si="1"/>
-        <v>5400000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -2485,10 +2479,10 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -2497,11 +2491,11 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2510,19 +2504,19 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="J51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>300000</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -2553,10 +2547,10 @@
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -2565,11 +2559,11 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F53">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2578,19 +2572,19 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="J53">
         <f t="shared" si="1"/>
-        <v>300000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -2621,44 +2615,44 @@
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E55">
-        <v>0</v>
+        <v>305</v>
       </c>
       <c r="F55">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>310</v>
       </c>
       <c r="G55">
         <v>0</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>2800000</v>
       </c>
       <c r="J55">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3050000</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2667,11 +2661,11 @@
         <v>0</v>
       </c>
       <c r="E56">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F56">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2680,53 +2674,53 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>0</v>
+        <v>16500000</v>
       </c>
       <c r="J56">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>16500000</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E57">
-        <v>305</v>
+        <v>60</v>
       </c>
       <c r="F57">
         <f t="shared" si="0"/>
-        <v>310</v>
+        <v>60</v>
       </c>
       <c r="G57">
         <v>0</v>
       </c>
       <c r="H57">
-        <v>250000</v>
+        <v>0</v>
       </c>
       <c r="I57">
-        <v>2800000</v>
+        <v>1600000</v>
       </c>
       <c r="J57">
         <f t="shared" si="1"/>
-        <v>3050000</v>
+        <v>1600000</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2735,11 +2729,11 @@
         <v>0</v>
       </c>
       <c r="E58">
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="F58">
         <f t="shared" si="0"/>
-        <v>130</v>
+        <v>21</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -2748,19 +2742,19 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>16500000</v>
+        <v>7495800</v>
       </c>
       <c r="J58">
         <f t="shared" si="1"/>
-        <v>16500000</v>
+        <v>7495800</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2769,11 +2763,11 @@
         <v>0</v>
       </c>
       <c r="E59">
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="F59">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>132</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2782,19 +2776,19 @@
         <v>0</v>
       </c>
       <c r="I59">
-        <v>1600000</v>
+        <v>3960000</v>
       </c>
       <c r="J59">
         <f t="shared" si="1"/>
-        <v>1600000</v>
+        <v>3960000</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2803,11 +2797,11 @@
         <v>0</v>
       </c>
       <c r="E60">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F60">
         <f t="shared" si="0"/>
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G60">
         <v>0</v>
@@ -2816,19 +2810,19 @@
         <v>0</v>
       </c>
       <c r="I60">
-        <v>7495800</v>
+        <v>0</v>
       </c>
       <c r="J60">
         <f t="shared" si="1"/>
-        <v>7495800</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2837,11 +2831,11 @@
         <v>0</v>
       </c>
       <c r="E61">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <f t="shared" si="0"/>
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2850,19 +2844,19 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>3960000</v>
+        <v>0</v>
       </c>
       <c r="J61">
         <f t="shared" si="1"/>
-        <v>3960000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2893,10 +2887,10 @@
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2927,10 +2921,10 @@
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2961,10 +2955,10 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2973,11 +2967,11 @@
         <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F65">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -2986,19 +2980,19 @@
         <v>0</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="J65">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3007,11 +3001,11 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="F66">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f t="shared" ref="F66:F100" si="2">C66+D66+E66</f>
+        <v>60</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -3020,19 +3014,19 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="J66">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f t="shared" ref="J66:J100" si="3">G66+H66+I66</f>
+        <v>10000000</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -3041,11 +3035,11 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <f t="shared" si="0"/>
-        <v>10</v>
+        <f t="shared" si="2"/>
+        <v>0</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -3054,257 +3048,257 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="J67">
-        <f t="shared" si="1"/>
-        <v>10000000</v>
+        <f t="shared" si="3"/>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E68">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="F68">
-        <f t="shared" ref="F68:F103" si="2">C68+D68+E68</f>
-        <v>60</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="G68">
         <v>0</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="I68">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="J68">
-        <f t="shared" ref="J68:J103" si="3">G68+H68+I68</f>
-        <v>10000000</v>
+        <f t="shared" si="3"/>
+        <v>150000</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G69">
         <v>0</v>
       </c>
       <c r="H69">
-        <v>0</v>
+        <v>250000</v>
       </c>
       <c r="I69">
         <v>0</v>
       </c>
       <c r="J69">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
         <v>97</v>
       </c>
-      <c r="B70" t="s">
-        <v>43</v>
-      </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>42</v>
       </c>
       <c r="E70">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F70">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>86</v>
       </c>
       <c r="G70">
         <v>0</v>
       </c>
       <c r="H70">
-        <v>150000</v>
+        <v>16640000</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>10658000</v>
       </c>
       <c r="J70">
         <f t="shared" si="3"/>
-        <v>150000</v>
+        <v>27298000</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="F71">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="G71">
         <v>0</v>
       </c>
       <c r="H71">
-        <v>250000</v>
+        <v>4050000</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>3225000</v>
       </c>
       <c r="J71">
         <f t="shared" si="3"/>
-        <v>250000</v>
+        <v>7275000</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="E72">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="F72">
         <f t="shared" si="2"/>
-        <v>86</v>
+        <v>21</v>
       </c>
       <c r="G72">
         <v>0</v>
       </c>
       <c r="H72">
-        <v>16640000</v>
+        <v>400000</v>
       </c>
       <c r="I72">
-        <v>10658000</v>
+        <v>1190000</v>
       </c>
       <c r="J72">
         <f t="shared" si="3"/>
-        <v>27298000</v>
+        <v>1590000</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E73">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F73">
         <f t="shared" si="2"/>
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G73">
         <v>0</v>
       </c>
       <c r="H73">
-        <v>4050000</v>
+        <v>0</v>
       </c>
       <c r="I73">
-        <v>3225000</v>
+        <v>5050000</v>
       </c>
       <c r="J73">
         <f t="shared" si="3"/>
-        <v>7275000</v>
+        <v>5050000</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E74">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F74">
         <f t="shared" si="2"/>
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="G74">
         <v>0</v>
       </c>
       <c r="H74">
-        <v>400000</v>
+        <v>0</v>
       </c>
       <c r="I74">
-        <v>1190000</v>
+        <v>4000000</v>
       </c>
       <c r="J74">
         <f t="shared" si="3"/>
-        <v>1590000</v>
+        <v>4000000</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -3313,11 +3307,11 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="F75">
         <f t="shared" si="2"/>
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -3326,19 +3320,19 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>5050000</v>
+        <v>0</v>
       </c>
       <c r="J75">
         <f t="shared" si="3"/>
-        <v>5050000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3347,11 +3341,11 @@
         <v>0</v>
       </c>
       <c r="E76">
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="F76">
         <f t="shared" si="2"/>
-        <v>32</v>
+        <v>232</v>
       </c>
       <c r="G76">
         <v>0</v>
@@ -3360,19 +3354,19 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>4000000</v>
+        <v>11600000</v>
       </c>
       <c r="J76">
         <f t="shared" si="3"/>
-        <v>4000000</v>
+        <v>11600000</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -3403,10 +3397,10 @@
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -3415,11 +3409,11 @@
         <v>0</v>
       </c>
       <c r="E78">
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <f t="shared" si="2"/>
-        <v>232</v>
+        <v>0</v>
       </c>
       <c r="G78">
         <v>0</v>
@@ -3428,19 +3422,19 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>11600000</v>
+        <v>0</v>
       </c>
       <c r="J78">
         <f t="shared" si="3"/>
-        <v>11600000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -3471,10 +3465,10 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -3505,10 +3499,10 @@
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3539,10 +3533,10 @@
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -3573,10 +3567,10 @@
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -3607,10 +3601,10 @@
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -3641,10 +3635,10 @@
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -3675,10 +3669,10 @@
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3709,10 +3703,10 @@
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C87">
         <v>0</v>
@@ -3743,10 +3737,10 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -3777,10 +3771,10 @@
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -3789,11 +3783,11 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F89">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -3811,10 +3805,10 @@
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -3823,11 +3817,11 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F90">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="G90">
         <v>0</v>
@@ -3836,19 +3830,19 @@
         <v>0</v>
       </c>
       <c r="I90">
-        <v>0</v>
+        <v>20000000</v>
       </c>
       <c r="J90">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20000000</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -3879,10 +3873,10 @@
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -3891,11 +3885,11 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="F92">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>90</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -3904,19 +3898,19 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="J92">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>5000000</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -3925,11 +3919,11 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="F93">
         <f t="shared" si="2"/>
-        <v>230</v>
+        <v>600</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3938,19 +3932,19 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>20000000</v>
+        <v>25000000</v>
       </c>
       <c r="J93">
         <f t="shared" si="3"/>
-        <v>20000000</v>
+        <v>25000000</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -3959,11 +3953,11 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="F94">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -3972,19 +3966,19 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>0</v>
+        <v>2000000</v>
       </c>
       <c r="J94">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2000000</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -3993,11 +3987,11 @@
         <v>0</v>
       </c>
       <c r="E95">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <f t="shared" si="2"/>
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -4006,19 +4000,19 @@
         <v>0</v>
       </c>
       <c r="I95">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="J95">
         <f t="shared" si="3"/>
-        <v>5000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4027,11 +4021,11 @@
         <v>0</v>
       </c>
       <c r="E96">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="F96">
         <f t="shared" si="2"/>
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="G96">
         <v>0</v>
@@ -4040,19 +4034,19 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>25000000</v>
+        <v>250000</v>
       </c>
       <c r="J96">
         <f t="shared" si="3"/>
-        <v>25000000</v>
+        <v>250000</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -4061,11 +4055,11 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="F97">
         <f t="shared" si="2"/>
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -4074,19 +4068,19 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>2000000</v>
+        <v>2100000</v>
       </c>
       <c r="J97">
         <f t="shared" si="3"/>
-        <v>2000000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -4095,11 +4089,11 @@
         <v>0</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="F98">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -4108,19 +4102,19 @@
         <v>0</v>
       </c>
       <c r="I98">
-        <v>0</v>
+        <v>9600000</v>
       </c>
       <c r="J98">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>9600000</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -4129,11 +4123,11 @@
         <v>0</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="F99">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>117</v>
       </c>
       <c r="G99">
         <v>0</v>
@@ -4142,145 +4136,43 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>250000</v>
+        <v>2340000</v>
       </c>
       <c r="J99">
         <f t="shared" si="3"/>
-        <v>250000</v>
+        <v>2340000</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E100">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="F100">
         <f t="shared" si="2"/>
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="G100">
         <v>0</v>
       </c>
       <c r="H100">
-        <v>0</v>
+        <v>630000</v>
       </c>
       <c r="I100">
-        <v>2100000</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <f t="shared" si="3"/>
-        <v>2100000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>98</v>
-      </c>
-      <c r="B101" t="s">
-        <v>80</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>186</v>
-      </c>
-      <c r="F101">
-        <f t="shared" si="2"/>
-        <v>186</v>
-      </c>
-      <c r="G101">
-        <v>0</v>
-      </c>
-      <c r="H101">
-        <v>0</v>
-      </c>
-      <c r="I101">
-        <v>9600000</v>
-      </c>
-      <c r="J101">
-        <f t="shared" si="3"/>
-        <v>9600000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
-        <v>81</v>
-      </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <v>117</v>
-      </c>
-      <c r="F102">
-        <f t="shared" si="2"/>
-        <v>117</v>
-      </c>
-      <c r="G102">
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <v>0</v>
-      </c>
-      <c r="I102">
-        <v>2340000</v>
-      </c>
-      <c r="J102">
-        <f t="shared" si="3"/>
-        <v>2340000</v>
-      </c>
-    </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>98</v>
-      </c>
-      <c r="B103" t="s">
-        <v>82</v>
-      </c>
-      <c r="C103">
-        <v>0</v>
-      </c>
-      <c r="D103">
-        <v>21</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-      <c r="F103">
-        <f t="shared" si="2"/>
-        <v>21</v>
-      </c>
-      <c r="G103">
-        <v>0</v>
-      </c>
-      <c r="H103">
-        <v>630000</v>
-      </c>
-      <c r="I103">
-        <v>0</v>
-      </c>
-      <c r="J103">
         <f t="shared" si="3"/>
         <v>630000</v>
       </c>
@@ -4296,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4196D461-2F81-4E04-8775-526A4FCFC2F8}">
-  <dimension ref="A1:H103"/>
+  <dimension ref="A1:H100"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
@@ -4308,51 +4200,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C1" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="H1" s="4"/>
+      <c r="C1" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F1" s="5"/>
+      <c r="G1" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="H1" s="6"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" t="s">
         <v>86</v>
       </c>
-      <c r="C2" t="s">
-        <v>93</v>
-      </c>
       <c r="D2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="E2" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>128</v>
+        <v>87</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -4377,10 +4269,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -4395,17 +4287,17 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <f t="shared" ref="G4:G67" si="0">C4+E4</f>
+        <f t="shared" ref="G4:G65" si="0">C4+E4</f>
         <v>0</v>
       </c>
       <c r="H4">
-        <f t="shared" ref="H4:H67" si="1">D4+F4</f>
+        <f t="shared" ref="H4:H65" si="1">D4+F4</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B5" t="s">
         <v>0</v>
@@ -4433,10 +4325,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -4461,10 +4353,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -4489,10 +4381,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -4517,10 +4409,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>122</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -4545,7 +4437,7 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>2</v>
@@ -4573,7 +4465,7 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
         <v>3</v>
@@ -4601,7 +4493,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
@@ -4629,10 +4521,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>235</v>
@@ -4657,10 +4549,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -4685,7 +4577,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -4713,7 +4605,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -4741,7 +4633,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -4769,10 +4661,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -4797,10 +4689,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="C19">
         <v>400</v>
@@ -4825,7 +4717,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -4853,10 +4745,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C21">
         <v>9</v>
@@ -4881,10 +4773,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -4909,7 +4801,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B23" t="s">
         <v>8</v>
@@ -4937,10 +4829,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B24" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C24">
         <v>1.25</v>
@@ -4965,7 +4857,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B25" t="s">
         <v>9</v>
@@ -4993,10 +4885,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -5021,10 +4913,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5049,10 +4941,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -5077,10 +4969,10 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -5105,10 +4997,10 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -5133,10 +5025,10 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5161,10 +5053,10 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B32" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5189,10 +5081,10 @@
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -5217,10 +5109,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -5245,10 +5137,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -5273,10 +5165,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -5301,35 +5193,35 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>48750000</v>
       </c>
       <c r="E37">
-        <v>0</v>
+        <v>1425</v>
       </c>
       <c r="F37">
-        <v>0</v>
+        <v>117562500</v>
       </c>
       <c r="G37">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="H37">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>166312500</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B38" t="s">
         <v>18</v>
@@ -5357,38 +5249,38 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="C39">
-        <v>375</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>48750000</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>1425</v>
+        <v>198</v>
       </c>
       <c r="F39">
-        <v>117562500</v>
+        <v>16335000</v>
       </c>
       <c r="G39">
         <f t="shared" si="0"/>
-        <v>1800</v>
+        <v>198</v>
       </c>
       <c r="H39">
         <f t="shared" si="1"/>
-        <v>166312500</v>
+        <v>16335000</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -5397,54 +5289,54 @@
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0</v>
+        <v>3620.36</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>78811616.840000004</v>
       </c>
       <c r="G40">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3620.36</v>
       </c>
       <c r="H40">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>78811616.840000004</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>27.9</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1198109.7</v>
       </c>
       <c r="E41">
-        <v>198</v>
+        <v>1580.16</v>
       </c>
       <c r="F41">
-        <v>16335000</v>
+        <v>34398503.039999999</v>
       </c>
       <c r="G41">
         <f t="shared" si="0"/>
-        <v>198</v>
+        <v>1608.0600000000002</v>
       </c>
       <c r="H41">
         <f t="shared" si="1"/>
-        <v>16335000</v>
+        <v>35596612.740000002</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -5453,222 +5345,222 @@
         <v>0</v>
       </c>
       <c r="E42">
-        <v>3620.36</v>
+        <v>1400.12</v>
       </c>
       <c r="F42">
-        <v>78811616.840000004</v>
+        <v>30479212.280000001</v>
       </c>
       <c r="G42">
         <f t="shared" si="0"/>
-        <v>3620.36</v>
+        <v>1400.12</v>
       </c>
       <c r="H42">
         <f t="shared" si="1"/>
-        <v>78811616.840000004</v>
+        <v>30479212.280000001</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C43">
-        <v>27.9</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>1198109.7</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>1580.16</v>
+        <v>4200.38</v>
       </c>
       <c r="F43">
-        <v>34398503.039999999</v>
+        <v>91438072.219999999</v>
       </c>
       <c r="G43">
         <f t="shared" si="0"/>
-        <v>1608.0600000000002</v>
+        <v>4200.38</v>
       </c>
       <c r="H43">
         <f t="shared" si="1"/>
-        <v>35596612.740000002</v>
+        <v>91438072.219999999</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>32.549999999999997</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1397794.65</v>
       </c>
       <c r="E44">
-        <v>1400.12</v>
+        <v>1960.18</v>
       </c>
       <c r="F44">
-        <v>30479212.280000001</v>
+        <v>42671158.420000002</v>
       </c>
       <c r="G44">
         <f t="shared" si="0"/>
-        <v>1400.12</v>
+        <v>1992.73</v>
       </c>
       <c r="H44">
         <f t="shared" si="1"/>
-        <v>30479212.280000001</v>
+        <v>44068953.07</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>55.81</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>2396648.83</v>
       </c>
       <c r="E45">
-        <v>4200.38</v>
+        <v>3360.31</v>
       </c>
       <c r="F45">
-        <v>91438072.219999999</v>
+        <v>73150588.390000001</v>
       </c>
       <c r="G45">
         <f t="shared" si="0"/>
-        <v>4200.38</v>
+        <v>3416.12</v>
       </c>
       <c r="H45">
         <f t="shared" si="1"/>
-        <v>91438072.219999999</v>
+        <v>75547237.219999999</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B46" t="s">
-        <v>25</v>
+        <v>115</v>
       </c>
       <c r="C46">
-        <v>32.549999999999997</v>
+        <v>57.81</v>
       </c>
       <c r="D46">
-        <v>1397794.65</v>
+        <v>2482534.83</v>
       </c>
       <c r="E46">
-        <v>1960.18</v>
+        <v>3660.31</v>
       </c>
       <c r="F46">
-        <v>42671158.420000002</v>
+        <v>79681288.390000001</v>
       </c>
       <c r="G46">
         <f t="shared" si="0"/>
-        <v>1992.73</v>
+        <v>3718.12</v>
       </c>
       <c r="H46">
         <f t="shared" si="1"/>
-        <v>44068953.07</v>
+        <v>82163823.219999999</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B47" t="s">
         <v>24</v>
       </c>
       <c r="C47">
-        <v>55.81</v>
+        <v>25.9</v>
       </c>
       <c r="D47">
-        <v>2396648.83</v>
+        <v>1112223.7</v>
       </c>
       <c r="E47">
-        <v>3360.31</v>
+        <v>1780.16</v>
       </c>
       <c r="F47">
-        <v>73150588.390000001</v>
+        <v>38752303.039999999</v>
       </c>
       <c r="G47">
         <f t="shared" si="0"/>
-        <v>3416.12</v>
+        <v>1806.0600000000002</v>
       </c>
       <c r="H47">
         <f t="shared" si="1"/>
-        <v>75547237.219999999</v>
+        <v>39864526.740000002</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>44</v>
       </c>
       <c r="C48">
-        <v>57.81</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2482534.83</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>3660.31</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>79681288.390000001</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <f t="shared" si="0"/>
-        <v>3718.12</v>
+        <v>0</v>
       </c>
       <c r="H48">
         <f t="shared" si="1"/>
-        <v>82163823.219999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>117</v>
       </c>
       <c r="C49">
-        <v>25.9</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1112223.7</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>1780.16</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>38752303.039999999</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <f t="shared" si="0"/>
-        <v>1806.0600000000002</v>
+        <v>0</v>
       </c>
       <c r="H49">
         <f t="shared" si="1"/>
-        <v>39864526.740000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -5677,26 +5569,26 @@
         <v>0</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>23000000</v>
       </c>
       <c r="G50">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="H50">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>23000000</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B51" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -5705,26 +5597,26 @@
         <v>0</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>8233044</v>
       </c>
       <c r="G51">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="H51">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>8233044</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B52" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -5733,26 +5625,26 @@
         <v>0</v>
       </c>
       <c r="E52">
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="F52">
-        <v>23000000</v>
+        <v>4190500</v>
       </c>
       <c r="G52">
         <f t="shared" si="0"/>
-        <v>2300</v>
+        <v>500</v>
       </c>
       <c r="H52">
         <f t="shared" si="1"/>
-        <v>23000000</v>
+        <v>4190500</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B53" t="s">
-        <v>29</v>
+        <v>116</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -5761,26 +5653,26 @@
         <v>0</v>
       </c>
       <c r="E53">
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="F53">
-        <v>8233044</v>
+        <v>11500000</v>
       </c>
       <c r="G53">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>500</v>
       </c>
       <c r="H53">
         <f t="shared" si="1"/>
-        <v>8233044</v>
+        <v>11500000</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B54" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -5789,88 +5681,88 @@
         <v>0</v>
       </c>
       <c r="E54">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F54">
-        <v>4190500</v>
+        <v>7000000</v>
       </c>
       <c r="G54">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H54">
         <f t="shared" si="1"/>
-        <v>4190500</v>
+        <v>7000000</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B55" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>3214.77</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>243880006.91</v>
       </c>
       <c r="E55">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F55">
-        <v>11500000</v>
+        <v>0</v>
       </c>
       <c r="G55">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>3214.77</v>
       </c>
       <c r="H55">
         <f t="shared" si="1"/>
-        <v>11500000</v>
+        <v>243880006.91</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1159.7</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>118457997.19</v>
       </c>
       <c r="E56">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F56">
-        <v>7000000</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1159.7</v>
       </c>
       <c r="H56">
         <f t="shared" si="1"/>
-        <v>7000000</v>
+        <v>118457997.19</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>120</v>
+        <v>35</v>
       </c>
       <c r="C57">
-        <v>3214.77</v>
+        <v>146</v>
       </c>
       <c r="D57">
-        <v>243880006.91</v>
+        <v>5278069.3600000003</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -5880,25 +5772,25 @@
       </c>
       <c r="G57">
         <f t="shared" si="0"/>
-        <v>3214.77</v>
+        <v>146</v>
       </c>
       <c r="H57">
         <f t="shared" si="1"/>
-        <v>243880006.91</v>
+        <v>5278069.3600000003</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B58" t="s">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="C58">
-        <v>1159.7</v>
+        <v>118.67</v>
       </c>
       <c r="D58">
-        <v>118457997.19</v>
+        <v>14774100.52</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -5908,25 +5800,25 @@
       </c>
       <c r="G58">
         <f t="shared" si="0"/>
-        <v>1159.7</v>
+        <v>118.67</v>
       </c>
       <c r="H58">
         <f t="shared" si="1"/>
-        <v>118457997.19</v>
+        <v>14774100.52</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B59" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C59">
-        <v>146</v>
+        <v>164.5</v>
       </c>
       <c r="D59">
-        <v>5278069.3600000003</v>
+        <v>38124000.18</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -5936,25 +5828,25 @@
       </c>
       <c r="G59">
         <f t="shared" si="0"/>
-        <v>146</v>
+        <v>164.5</v>
       </c>
       <c r="H59">
         <f t="shared" si="1"/>
-        <v>5278069.3600000003</v>
+        <v>38124000.18</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B60" t="s">
-        <v>121</v>
+        <v>30</v>
       </c>
       <c r="C60">
-        <v>118.67</v>
+        <v>11.25</v>
       </c>
       <c r="D60">
-        <v>14774100.52</v>
+        <v>5062000.05</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -5964,25 +5856,25 @@
       </c>
       <c r="G60">
         <f t="shared" si="0"/>
-        <v>118.67</v>
+        <v>11.25</v>
       </c>
       <c r="H60">
         <f t="shared" si="1"/>
-        <v>14774100.52</v>
+        <v>5062000.05</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C61">
-        <v>164.5</v>
+        <v>49.5</v>
       </c>
       <c r="D61">
-        <v>38124000.18</v>
+        <v>22299999.98</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -5992,25 +5884,25 @@
       </c>
       <c r="G61">
         <f t="shared" si="0"/>
-        <v>164.5</v>
+        <v>49.5</v>
       </c>
       <c r="H61">
         <f t="shared" si="1"/>
-        <v>38124000.18</v>
+        <v>22299999.98</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B62" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C62">
-        <v>11.25</v>
+        <v>13.6</v>
       </c>
       <c r="D62">
-        <v>5062000.05</v>
+        <v>7650000</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -6020,25 +5912,25 @@
       </c>
       <c r="G62">
         <f t="shared" si="0"/>
-        <v>11.25</v>
+        <v>13.6</v>
       </c>
       <c r="H62">
         <f t="shared" si="1"/>
-        <v>5062000.05</v>
+        <v>7650000</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B63" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C63">
-        <v>49.5</v>
+        <v>19</v>
       </c>
       <c r="D63">
-        <v>22299999.98</v>
+        <v>9999000.0399999991</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -6048,75 +5940,75 @@
       </c>
       <c r="G63">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>19</v>
       </c>
       <c r="H63">
         <f t="shared" si="1"/>
-        <v>22299999.98</v>
+        <v>9999000.0399999991</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>94</v>
       </c>
       <c r="C64">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>7650000</v>
+        <v>0</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1536712</v>
       </c>
       <c r="G64">
         <f t="shared" si="0"/>
-        <v>13.6</v>
+        <v>94</v>
       </c>
       <c r="H64">
         <f t="shared" si="1"/>
-        <v>7650000</v>
+        <v>1536712</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>90</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="C65">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>9999000.0399999991</v>
+        <v>0</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>6579</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>8750070</v>
       </c>
       <c r="G65">
         <f t="shared" si="0"/>
-        <v>19</v>
+        <v>6579</v>
       </c>
       <c r="H65">
         <f t="shared" si="1"/>
-        <v>9999000.0399999991</v>
+        <v>8750070</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B66" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -6125,26 +6017,26 @@
         <v>0</v>
       </c>
       <c r="E66">
-        <v>94</v>
+        <v>748</v>
       </c>
       <c r="F66">
-        <v>1536712</v>
+        <v>9536042.5600000005</v>
       </c>
       <c r="G66">
-        <f t="shared" si="0"/>
-        <v>94</v>
+        <f t="shared" ref="G66:G100" si="2">C66+E66</f>
+        <v>748</v>
       </c>
       <c r="H66">
-        <f t="shared" si="1"/>
-        <v>1536712</v>
+        <f t="shared" ref="H66:H100" si="3">D66+F66</f>
+        <v>9536042.5600000005</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B67" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -6153,26 +6045,26 @@
         <v>0</v>
       </c>
       <c r="E67">
-        <v>6579</v>
+        <v>325</v>
       </c>
       <c r="F67">
-        <v>8750070</v>
+        <v>9826700</v>
       </c>
       <c r="G67">
-        <f t="shared" si="0"/>
-        <v>6579</v>
+        <f t="shared" si="2"/>
+        <v>325</v>
       </c>
       <c r="H67">
-        <f t="shared" si="1"/>
-        <v>8750070</v>
+        <f t="shared" si="3"/>
+        <v>9826700</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B68" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -6181,26 +6073,26 @@
         <v>0</v>
       </c>
       <c r="E68">
-        <v>748</v>
+        <v>440</v>
       </c>
       <c r="F68">
-        <v>9536042.5600000005</v>
+        <v>24054360</v>
       </c>
       <c r="G68">
-        <f t="shared" ref="G68:G103" si="2">C68+E68</f>
-        <v>748</v>
+        <f t="shared" si="2"/>
+        <v>440</v>
       </c>
       <c r="H68">
-        <f t="shared" ref="H68:H103" si="3">D68+F68</f>
-        <v>9536042.5600000005</v>
+        <f t="shared" si="3"/>
+        <v>24054360</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B69" t="s">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -6209,54 +6101,54 @@
         <v>0</v>
       </c>
       <c r="E69">
-        <v>325</v>
+        <v>217</v>
       </c>
       <c r="F69">
-        <v>9826700</v>
+        <v>14615998.109999999</v>
       </c>
       <c r="G69">
         <f t="shared" si="2"/>
-        <v>325</v>
+        <v>217</v>
       </c>
       <c r="H69">
         <f t="shared" si="3"/>
-        <v>9826700</v>
+        <v>14615998.109999999</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>90</v>
+      </c>
+      <c r="B70" t="s">
         <v>97</v>
       </c>
-      <c r="B70" t="s">
-        <v>43</v>
-      </c>
       <c r="C70">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>6000000</v>
       </c>
       <c r="E70">
-        <v>440</v>
+        <v>255</v>
       </c>
       <c r="F70">
-        <v>24054360</v>
+        <v>2425050</v>
       </c>
       <c r="G70">
         <f t="shared" si="2"/>
-        <v>440</v>
+        <v>555</v>
       </c>
       <c r="H70">
         <f t="shared" si="3"/>
-        <v>24054360</v>
+        <v>8425050</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -6265,54 +6157,54 @@
         <v>0</v>
       </c>
       <c r="E71">
-        <v>217</v>
+        <v>4734</v>
       </c>
       <c r="F71">
-        <v>14615998.109999999</v>
+        <v>37872000</v>
       </c>
       <c r="G71">
         <f t="shared" si="2"/>
-        <v>217</v>
+        <v>4734</v>
       </c>
       <c r="H71">
         <f t="shared" si="3"/>
-        <v>14615998.109999999</v>
+        <v>37872000</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>43</v>
       </c>
       <c r="C72">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>6000000</v>
+        <v>0</v>
       </c>
       <c r="E72">
-        <v>255</v>
+        <v>0</v>
       </c>
       <c r="F72">
-        <v>2425050</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <f t="shared" si="2"/>
-        <v>555</v>
+        <v>0</v>
       </c>
       <c r="H72">
         <f t="shared" si="3"/>
-        <v>8425050</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -6321,26 +6213,26 @@
         <v>0</v>
       </c>
       <c r="E73">
-        <v>4734</v>
+        <v>2445</v>
       </c>
       <c r="F73">
-        <v>37872000</v>
+        <v>12225000</v>
       </c>
       <c r="G73">
         <f t="shared" si="2"/>
-        <v>4734</v>
+        <v>2445</v>
       </c>
       <c r="H73">
         <f t="shared" si="3"/>
-        <v>37872000</v>
+        <v>12225000</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -6349,26 +6241,26 @@
         <v>0</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="F74">
-        <v>0</v>
+        <v>20749850</v>
       </c>
       <c r="G74">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1550</v>
       </c>
       <c r="H74">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>20749850</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>97</v>
+        <v>76</v>
       </c>
       <c r="B75" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -6377,54 +6269,54 @@
         <v>0</v>
       </c>
       <c r="E75">
-        <v>2445</v>
+        <v>0</v>
       </c>
       <c r="F75">
-        <v>12225000</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <f t="shared" si="2"/>
-        <v>2445</v>
+        <v>0</v>
       </c>
       <c r="H75">
         <f t="shared" si="3"/>
-        <v>12225000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>48.5</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>4056006.5</v>
       </c>
       <c r="E76">
-        <v>1550</v>
+        <v>0</v>
       </c>
       <c r="F76">
-        <v>20749850</v>
+        <v>0</v>
       </c>
       <c r="G76">
         <f t="shared" si="2"/>
-        <v>1550</v>
+        <v>48.5</v>
       </c>
       <c r="H76">
         <f t="shared" si="3"/>
-        <v>20749850</v>
+        <v>4056006.5</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -6449,16 +6341,16 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C78">
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>4056006.5</v>
+        <v>0</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -6468,19 +6360,19 @@
       </c>
       <c r="G78">
         <f t="shared" si="2"/>
-        <v>48.5</v>
+        <v>0</v>
       </c>
       <c r="H78">
         <f t="shared" si="3"/>
-        <v>4056006.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -6505,10 +6397,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B80" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -6533,10 +6425,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -6561,10 +6453,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -6589,10 +6481,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B83" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -6617,10 +6509,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B84" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -6629,26 +6521,26 @@
         <v>0</v>
       </c>
       <c r="E84">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="F84">
-        <v>0</v>
+        <v>4860000</v>
       </c>
       <c r="G84">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="H84">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>4860000</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C85">
         <v>0</v>
@@ -6673,10 +6565,10 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -6685,54 +6577,54 @@
         <v>0</v>
       </c>
       <c r="E86">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>4860000</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <f t="shared" si="2"/>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H86">
         <f t="shared" si="3"/>
-        <v>4860000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>985855</v>
       </c>
       <c r="E87">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F87">
-        <v>0</v>
+        <v>1078500</v>
       </c>
       <c r="G87">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="H87">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>2064355</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="B88" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C88">
         <v>0</v>
@@ -6757,38 +6649,38 @@
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B89" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="C89">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>985855</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>30</v>
+        <v>1687</v>
       </c>
       <c r="F89">
-        <v>1078500</v>
+        <v>33740000</v>
       </c>
       <c r="G89">
         <f t="shared" si="2"/>
-        <v>43</v>
+        <v>1687</v>
       </c>
       <c r="H89">
         <f t="shared" si="3"/>
-        <v>2064355</v>
+        <v>33740000</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -6797,26 +6689,26 @@
         <v>0</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>2273</v>
       </c>
       <c r="F90">
-        <v>0</v>
+        <v>45460000</v>
       </c>
       <c r="G90">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2273</v>
       </c>
       <c r="H90">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>45460000</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -6825,26 +6717,26 @@
         <v>0</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="F91">
-        <v>0</v>
+        <v>39600000</v>
       </c>
       <c r="G91">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1980</v>
       </c>
       <c r="H91">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>39600000</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B92" t="s">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -6853,26 +6745,26 @@
         <v>0</v>
       </c>
       <c r="E92">
-        <v>1687</v>
+        <v>2475</v>
       </c>
       <c r="F92">
-        <v>33740000</v>
+        <v>49500000</v>
       </c>
       <c r="G92">
         <f t="shared" si="2"/>
-        <v>1687</v>
+        <v>2475</v>
       </c>
       <c r="H92">
         <f t="shared" si="3"/>
-        <v>33740000</v>
+        <v>49500000</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B93" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -6881,26 +6773,26 @@
         <v>0</v>
       </c>
       <c r="E93">
-        <v>2273</v>
+        <v>1990</v>
       </c>
       <c r="F93">
-        <v>45460000</v>
+        <v>39800000</v>
       </c>
       <c r="G93">
         <f t="shared" si="2"/>
-        <v>2273</v>
+        <v>1990</v>
       </c>
       <c r="H93">
         <f t="shared" si="3"/>
-        <v>45460000</v>
+        <v>39800000</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B94" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -6909,144 +6801,144 @@
         <v>0</v>
       </c>
       <c r="E94">
-        <v>1980</v>
+        <v>2095</v>
       </c>
       <c r="F94">
-        <v>39600000</v>
+        <v>41900000</v>
       </c>
       <c r="G94">
         <f t="shared" si="2"/>
-        <v>1980</v>
+        <v>2095</v>
       </c>
       <c r="H94">
         <f t="shared" si="3"/>
-        <v>39600000</v>
+        <v>41900000</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="E95">
-        <v>2475</v>
+        <v>5</v>
       </c>
       <c r="F95">
-        <v>49500000</v>
+        <v>350000</v>
       </c>
       <c r="G95">
         <f t="shared" si="2"/>
-        <v>2475</v>
+        <v>6</v>
       </c>
       <c r="H95">
         <f t="shared" si="3"/>
-        <v>49500000</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>2500000</v>
       </c>
       <c r="E96">
-        <v>1990</v>
+        <v>0</v>
       </c>
       <c r="F96">
-        <v>39800000</v>
+        <v>0</v>
       </c>
       <c r="G96">
         <f t="shared" si="2"/>
-        <v>1990</v>
+        <v>25</v>
       </c>
       <c r="H96">
         <f t="shared" si="3"/>
-        <v>39800000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B97" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="E97">
-        <v>2095</v>
+        <v>0</v>
       </c>
       <c r="F97">
-        <v>41900000</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <f t="shared" si="2"/>
-        <v>2095</v>
+        <v>5</v>
       </c>
       <c r="H97">
         <f t="shared" si="3"/>
-        <v>41900000</v>
+        <v>500000</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B98" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="E98">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="F98">
-        <v>350000</v>
+        <v>2500000</v>
       </c>
       <c r="G98">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H98">
         <f t="shared" si="3"/>
-        <v>450000</v>
+        <v>2500000</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C99">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>2500000</v>
+        <v>0</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -7056,25 +6948,25 @@
       </c>
       <c r="G99">
         <f t="shared" si="2"/>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H99">
         <f t="shared" si="3"/>
-        <v>2500000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B100" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="C100">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D100">
-        <v>500000</v>
+        <v>900000</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -7084,93 +6976,9 @@
       </c>
       <c r="G100">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H100">
-        <f t="shared" si="3"/>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>98</v>
-      </c>
-      <c r="B101" t="s">
-        <v>80</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
-      </c>
-      <c r="D101">
-        <v>0</v>
-      </c>
-      <c r="E101">
-        <v>50</v>
-      </c>
-      <c r="F101">
-        <v>2500000</v>
-      </c>
-      <c r="G101">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="H101">
-        <f t="shared" si="3"/>
-        <v>2500000</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>98</v>
-      </c>
-      <c r="B102" t="s">
-        <v>81</v>
-      </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
-      <c r="D102">
-        <v>0</v>
-      </c>
-      <c r="E102">
-        <v>0</v>
-      </c>
-      <c r="F102">
-        <v>0</v>
-      </c>
-      <c r="G102">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H102">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>98</v>
-      </c>
-      <c r="B103" t="s">
-        <v>82</v>
-      </c>
-      <c r="C103">
-        <v>9</v>
-      </c>
-      <c r="D103">
-        <v>900000</v>
-      </c>
-      <c r="E103">
-        <v>0</v>
-      </c>
-      <c r="F103">
-        <v>0</v>
-      </c>
-      <c r="G103">
-        <f t="shared" si="2"/>
-        <v>9</v>
-      </c>
-      <c r="H103">
         <f t="shared" si="3"/>
         <v>900000</v>
       </c>
